--- a/data/NPL_после2019.xlsx
+++ b/data/NPL_после2019.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Образование\Магистратура\Диплом\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Образование\Магистратура\Диплом\ITMO_NIR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F80A1F4D-FBC6-43CF-93F8-5FD537041169}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68599D37-DE19-4B36-9EC8-876939EB95BB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="3855" windowWidth="19455" windowHeight="11715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="в рублях" sheetId="1" r:id="rId1"/>
@@ -7230,7 +7230,7 @@
   <dimension ref="A1:CD28"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="139.42578125" customWidth="1"/>
+    <col min="1" max="1" width="32.5703125" customWidth="1"/>
     <col min="2" max="82" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -27394,14 +27394,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:CD28"/>
+  <dimension ref="A1:CH28"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="139.42578125" customWidth="1"/>
     <col min="2" max="82" width="22.5703125" customWidth="1"/>
+    <col min="83" max="86" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:82" s="1" customFormat="1" ht="78.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:86" s="1" customFormat="1" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>31</v>
       </c>
@@ -27410,7 +27411,7 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:82" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:86" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -27657,8 +27658,20 @@
       <c r="CD2" s="3">
         <v>45931</v>
       </c>
+      <c r="CE2" s="3">
+        <v>45962</v>
+      </c>
+      <c r="CF2" s="3">
+        <v>45992</v>
+      </c>
+      <c r="CG2" s="3">
+        <v>46023</v>
+      </c>
+      <c r="CH2" s="3">
+        <v>46054</v>
+      </c>
     </row>
-    <row r="3" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -27905,8 +27918,20 @@
       <c r="CD3" s="5">
         <v>80744404</v>
       </c>
+      <c r="CE3" s="5">
+        <v>82716928</v>
+      </c>
+      <c r="CF3" s="5">
+        <v>83998237</v>
+      </c>
+      <c r="CG3" s="5">
+        <v>84950836</v>
+      </c>
+      <c r="CH3" s="5">
+        <v>84081503</v>
+      </c>
     </row>
-    <row r="4" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -28153,8 +28178,20 @@
       <c r="CD4" s="5">
         <v>5399229</v>
       </c>
+      <c r="CE4" s="5">
+        <v>5581747</v>
+      </c>
+      <c r="CF4" s="5">
+        <v>5618512</v>
+      </c>
+      <c r="CG4" s="5">
+        <v>5673312</v>
+      </c>
+      <c r="CH4" s="5">
+        <v>5638475</v>
+      </c>
     </row>
-    <row r="5" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -28401,8 +28438,20 @@
       <c r="CD5" s="5">
         <v>3646205</v>
       </c>
+      <c r="CE5" s="5">
+        <v>3685311</v>
+      </c>
+      <c r="CF5" s="5">
+        <v>3700921</v>
+      </c>
+      <c r="CG5" s="5">
+        <v>3738085</v>
+      </c>
+      <c r="CH5" s="5">
+        <v>3663794</v>
+      </c>
     </row>
-    <row r="6" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -28649,8 +28698,20 @@
       <c r="CD6" s="5">
         <v>20644833</v>
       </c>
+      <c r="CE6" s="5">
+        <v>21204893</v>
+      </c>
+      <c r="CF6" s="5">
+        <v>21748203</v>
+      </c>
+      <c r="CG6" s="5">
+        <v>22454068</v>
+      </c>
+      <c r="CH6" s="5">
+        <v>22123253</v>
+      </c>
     </row>
-    <row r="7" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
@@ -28897,8 +28958,20 @@
       <c r="CD7" s="5">
         <v>1871118</v>
       </c>
+      <c r="CE7" s="5">
+        <v>1931642</v>
+      </c>
+      <c r="CF7" s="5">
+        <v>1982399</v>
+      </c>
+      <c r="CG7" s="5">
+        <v>2007124</v>
+      </c>
+      <c r="CH7" s="5">
+        <v>2012919</v>
+      </c>
     </row>
-    <row r="8" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -29145,8 +29218,20 @@
       <c r="CD8" s="5">
         <v>161529</v>
       </c>
+      <c r="CE8" s="5">
+        <v>161540</v>
+      </c>
+      <c r="CF8" s="5">
+        <v>162166</v>
+      </c>
+      <c r="CG8" s="5">
+        <v>165063</v>
+      </c>
+      <c r="CH8" s="5">
+        <v>164913</v>
+      </c>
     </row>
-    <row r="9" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
@@ -29393,8 +29478,20 @@
       <c r="CD9" s="5">
         <v>519746</v>
       </c>
+      <c r="CE9" s="5">
+        <v>515866</v>
+      </c>
+      <c r="CF9" s="5">
+        <v>507926</v>
+      </c>
+      <c r="CG9" s="5">
+        <v>509858</v>
+      </c>
+      <c r="CH9" s="5">
+        <v>505131</v>
+      </c>
     </row>
-    <row r="10" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
@@ -29641,8 +29738,20 @@
       <c r="CD10" s="5">
         <v>4154320</v>
       </c>
+      <c r="CE10" s="5">
+        <v>4218449</v>
+      </c>
+      <c r="CF10" s="5">
+        <v>4232583</v>
+      </c>
+      <c r="CG10" s="5">
+        <v>4366319</v>
+      </c>
+      <c r="CH10" s="5">
+        <v>4441784</v>
+      </c>
     </row>
-    <row r="11" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -29889,8 +29998,20 @@
       <c r="CD11" s="5">
         <v>4537070</v>
       </c>
+      <c r="CE11" s="5">
+        <v>4654621</v>
+      </c>
+      <c r="CF11" s="5">
+        <v>4804910</v>
+      </c>
+      <c r="CG11" s="5">
+        <v>5019038</v>
+      </c>
+      <c r="CH11" s="5">
+        <v>5044412</v>
+      </c>
     </row>
-    <row r="12" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -30137,8 +30258,20 @@
       <c r="CD12" s="5">
         <v>375133</v>
       </c>
+      <c r="CE12" s="5">
+        <v>378125</v>
+      </c>
+      <c r="CF12" s="5">
+        <v>383244</v>
+      </c>
+      <c r="CG12" s="5">
+        <v>393496</v>
+      </c>
+      <c r="CH12" s="5">
+        <v>400724</v>
+      </c>
     </row>
-    <row r="13" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
@@ -30385,8 +30518,20 @@
       <c r="CD13" s="5">
         <v>3344721</v>
       </c>
+      <c r="CE13" s="5">
+        <v>3386055</v>
+      </c>
+      <c r="CF13" s="5">
+        <v>3462404</v>
+      </c>
+      <c r="CG13" s="5">
+        <v>3531993</v>
+      </c>
+      <c r="CH13" s="5">
+        <v>3419787</v>
+      </c>
     </row>
-    <row r="14" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>12</v>
       </c>
@@ -30633,8 +30778,20 @@
       <c r="CD14" s="5">
         <v>1177443</v>
       </c>
+      <c r="CE14" s="5">
+        <v>1294923</v>
+      </c>
+      <c r="CF14" s="5">
+        <v>1341800</v>
+      </c>
+      <c r="CG14" s="5">
+        <v>1448427</v>
+      </c>
+      <c r="CH14" s="5">
+        <v>1349563</v>
+      </c>
     </row>
-    <row r="15" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
@@ -30881,8 +31038,20 @@
       <c r="CD15" s="5">
         <v>41062</v>
       </c>
+      <c r="CE15" s="5">
+        <v>41103</v>
+      </c>
+      <c r="CF15" s="5">
+        <v>41390</v>
+      </c>
+      <c r="CG15" s="5">
+        <v>43575</v>
+      </c>
+      <c r="CH15" s="5">
+        <v>35648</v>
+      </c>
     </row>
-    <row r="16" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>14</v>
       </c>
@@ -31129,8 +31298,20 @@
       <c r="CD16" s="5">
         <v>2731321</v>
       </c>
+      <c r="CE16" s="5">
+        <v>2793011</v>
+      </c>
+      <c r="CF16" s="5">
+        <v>2846381</v>
+      </c>
+      <c r="CG16" s="5">
+        <v>2904805</v>
+      </c>
+      <c r="CH16" s="5">
+        <v>2697655</v>
+      </c>
     </row>
-    <row r="17" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>15</v>
       </c>
@@ -31377,8 +31558,20 @@
       <c r="CD17" s="5">
         <v>456710</v>
       </c>
+      <c r="CE17" s="5">
+        <v>486943</v>
+      </c>
+      <c r="CF17" s="5">
+        <v>513622</v>
+      </c>
+      <c r="CG17" s="5">
+        <v>522421</v>
+      </c>
+      <c r="CH17" s="5">
+        <v>538020</v>
+      </c>
     </row>
-    <row r="18" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
@@ -31625,8 +31818,20 @@
       <c r="CD18" s="5">
         <v>1685212</v>
       </c>
+      <c r="CE18" s="5">
+        <v>1731527</v>
+      </c>
+      <c r="CF18" s="5">
+        <v>1782822</v>
+      </c>
+      <c r="CG18" s="5">
+        <v>1865237</v>
+      </c>
+      <c r="CH18" s="5">
+        <v>1847581</v>
+      </c>
     </row>
-    <row r="19" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
@@ -31873,8 +32078,20 @@
       <c r="CD19" s="5">
         <v>3027886</v>
       </c>
+      <c r="CE19" s="5">
+        <v>3041531</v>
+      </c>
+      <c r="CF19" s="5">
+        <v>3052543</v>
+      </c>
+      <c r="CG19" s="5">
+        <v>3094879</v>
+      </c>
+      <c r="CH19" s="5">
+        <v>3093928</v>
+      </c>
     </row>
-    <row r="20" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>18</v>
       </c>
@@ -32121,8 +32338,20 @@
       <c r="CD20" s="5">
         <v>2989423</v>
       </c>
+      <c r="CE20" s="5">
+        <v>3003048</v>
+      </c>
+      <c r="CF20" s="5">
+        <v>3014087</v>
+      </c>
+      <c r="CG20" s="5">
+        <v>3056079</v>
+      </c>
+      <c r="CH20" s="5">
+        <v>3055477</v>
+      </c>
     </row>
-    <row r="21" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>19</v>
       </c>
@@ -32369,8 +32598,20 @@
       <c r="CD21" s="5">
         <v>5052981</v>
       </c>
+      <c r="CE21" s="5">
+        <v>5185242</v>
+      </c>
+      <c r="CF21" s="5">
+        <v>5226062</v>
+      </c>
+      <c r="CG21" s="5">
+        <v>5119062</v>
+      </c>
+      <c r="CH21" s="5">
+        <v>5065026</v>
+      </c>
     </row>
-    <row r="22" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>20</v>
       </c>
@@ -32617,8 +32858,20 @@
       <c r="CD22" s="5">
         <v>4682063</v>
       </c>
+      <c r="CE22" s="5">
+        <v>4807978</v>
+      </c>
+      <c r="CF22" s="5">
+        <v>4848877</v>
+      </c>
+      <c r="CG22" s="5">
+        <v>4753483</v>
+      </c>
+      <c r="CH22" s="5">
+        <v>4710187</v>
+      </c>
     </row>
-    <row r="23" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>21</v>
       </c>
@@ -32865,8 +33118,20 @@
       <c r="CD23" s="5">
         <v>4741811</v>
       </c>
+      <c r="CE23" s="5">
+        <v>4853738</v>
+      </c>
+      <c r="CF23" s="5">
+        <v>4908113</v>
+      </c>
+      <c r="CG23" s="5">
+        <v>5085762</v>
+      </c>
+      <c r="CH23" s="5">
+        <v>5047307</v>
+      </c>
     </row>
-    <row r="24" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>22</v>
       </c>
@@ -33113,8 +33378,20 @@
       <c r="CD24" s="5">
         <v>113911</v>
       </c>
+      <c r="CE24" s="5">
+        <v>114290</v>
+      </c>
+      <c r="CF24" s="5">
+        <v>113144</v>
+      </c>
+      <c r="CG24" s="5">
+        <v>122813</v>
+      </c>
+      <c r="CH24" s="5">
+        <v>138993</v>
+      </c>
     </row>
-    <row r="25" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>23</v>
       </c>
@@ -33361,8 +33638,20 @@
       <c r="CD25" s="5">
         <v>7536237</v>
       </c>
+      <c r="CE25" s="5">
+        <v>7868796</v>
+      </c>
+      <c r="CF25" s="5">
+        <v>8213051</v>
+      </c>
+      <c r="CG25" s="5">
+        <v>8140169</v>
+      </c>
+      <c r="CH25" s="5">
+        <v>8153732</v>
+      </c>
     </row>
-    <row r="26" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>24</v>
       </c>
@@ -33609,8 +33898,20 @@
       <c r="CD26" s="5">
         <v>16626820</v>
       </c>
+      <c r="CE26" s="5">
+        <v>17059825</v>
+      </c>
+      <c r="CF26" s="5">
+        <v>17336433</v>
+      </c>
+      <c r="CG26" s="5">
+        <v>17230088</v>
+      </c>
+      <c r="CH26" s="5">
+        <v>16998011</v>
+      </c>
     </row>
-    <row r="27" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>25</v>
       </c>
@@ -33857,8 +34158,20 @@
       <c r="CD27" s="5">
         <v>15567401</v>
       </c>
+      <c r="CE27" s="5">
+        <v>15741828</v>
+      </c>
+      <c r="CF27" s="5">
+        <v>15675500</v>
+      </c>
+      <c r="CG27" s="5">
+        <v>15886881</v>
+      </c>
+      <c r="CH27" s="5">
+        <v>15672541</v>
+      </c>
     </row>
-    <row r="28" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>26</v>
       </c>
@@ -34104,6 +34417,18 @@
       </c>
       <c r="CD28" s="5">
         <v>461994</v>
+      </c>
+      <c r="CE28" s="5">
+        <v>447800</v>
+      </c>
+      <c r="CF28" s="5">
+        <v>436998</v>
+      </c>
+      <c r="CG28" s="5">
+        <v>401379</v>
+      </c>
+      <c r="CH28" s="5">
+        <v>441649</v>
       </c>
     </row>
   </sheetData>
@@ -34115,14 +34440,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:CD28"/>
+  <dimension ref="A1:CH28"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="139.42578125" customWidth="1"/>
     <col min="2" max="82" width="22.5703125" customWidth="1"/>
+    <col min="83" max="86" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:82" s="1" customFormat="1" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:86" s="1" customFormat="1" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>32</v>
       </c>
@@ -34131,7 +34457,7 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:82" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:86" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -34378,8 +34704,20 @@
       <c r="CD2" s="3">
         <v>45931</v>
       </c>
+      <c r="CE2" s="3">
+        <v>45962</v>
+      </c>
+      <c r="CF2" s="3">
+        <v>45992</v>
+      </c>
+      <c r="CG2" s="3">
+        <v>46023</v>
+      </c>
+      <c r="CH2" s="3">
+        <v>46054</v>
+      </c>
     </row>
-    <row r="3" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -34626,8 +34964,20 @@
       <c r="CD3" s="5">
         <v>2881803</v>
       </c>
+      <c r="CE3" s="5">
+        <v>2955877</v>
+      </c>
+      <c r="CF3" s="5">
+        <v>3031326</v>
+      </c>
+      <c r="CG3" s="5">
+        <v>2876832</v>
+      </c>
+      <c r="CH3" s="5">
+        <v>2918376</v>
+      </c>
     </row>
-    <row r="4" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -34874,8 +35224,20 @@
       <c r="CD4" s="5">
         <v>81524</v>
       </c>
+      <c r="CE4" s="5">
+        <v>78609</v>
+      </c>
+      <c r="CF4" s="5">
+        <v>77008</v>
+      </c>
+      <c r="CG4" s="5">
+        <v>81424</v>
+      </c>
+      <c r="CH4" s="5">
+        <v>62992</v>
+      </c>
     </row>
-    <row r="5" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -35122,8 +35484,20 @@
       <c r="CD5" s="5">
         <v>72911</v>
       </c>
+      <c r="CE5" s="5">
+        <v>69089</v>
+      </c>
+      <c r="CF5" s="5">
+        <v>68408</v>
+      </c>
+      <c r="CG5" s="5">
+        <v>72839</v>
+      </c>
+      <c r="CH5" s="5">
+        <v>54365</v>
+      </c>
     </row>
-    <row r="6" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -35370,8 +35744,20 @@
       <c r="CD6" s="5">
         <v>403544</v>
       </c>
+      <c r="CE6" s="5">
+        <v>425888</v>
+      </c>
+      <c r="CF6" s="5">
+        <v>430276</v>
+      </c>
+      <c r="CG6" s="5">
+        <v>429636</v>
+      </c>
+      <c r="CH6" s="5">
+        <v>450004</v>
+      </c>
     </row>
-    <row r="7" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
@@ -35618,8 +36004,20 @@
       <c r="CD7" s="5">
         <v>51084</v>
       </c>
+      <c r="CE7" s="5">
+        <v>49769</v>
+      </c>
+      <c r="CF7" s="5">
+        <v>52928</v>
+      </c>
+      <c r="CG7" s="5">
+        <v>44964</v>
+      </c>
+      <c r="CH7" s="5">
+        <v>45266</v>
+      </c>
     </row>
-    <row r="8" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -35866,8 +36264,20 @@
       <c r="CD8" s="5">
         <v>64351</v>
       </c>
+      <c r="CE8" s="5">
+        <v>64408</v>
+      </c>
+      <c r="CF8" s="5">
+        <v>64482</v>
+      </c>
+      <c r="CG8" s="5">
+        <v>64479</v>
+      </c>
+      <c r="CH8" s="5">
+        <v>64450</v>
+      </c>
     </row>
-    <row r="9" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
@@ -36114,8 +36524,20 @@
       <c r="CD9" s="5">
         <v>5377</v>
       </c>
+      <c r="CE9" s="5">
+        <v>6195</v>
+      </c>
+      <c r="CF9" s="5">
+        <v>6542</v>
+      </c>
+      <c r="CG9" s="5">
+        <v>8997</v>
+      </c>
+      <c r="CH9" s="5">
+        <v>9292</v>
+      </c>
     </row>
-    <row r="10" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
@@ -36362,8 +36784,20 @@
       <c r="CD10" s="5">
         <v>36447</v>
       </c>
+      <c r="CE10" s="5">
+        <v>49012</v>
+      </c>
+      <c r="CF10" s="5">
+        <v>47873</v>
+      </c>
+      <c r="CG10" s="5">
+        <v>52530</v>
+      </c>
+      <c r="CH10" s="5">
+        <v>63739</v>
+      </c>
     </row>
-    <row r="11" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
@@ -36610,8 +37044,20 @@
       <c r="CD11" s="5">
         <v>28790</v>
       </c>
+      <c r="CE11" s="5">
+        <v>26399</v>
+      </c>
+      <c r="CF11" s="5">
+        <v>23198</v>
+      </c>
+      <c r="CG11" s="5">
+        <v>23385</v>
+      </c>
+      <c r="CH11" s="5">
+        <v>23867</v>
+      </c>
     </row>
-    <row r="12" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -36858,8 +37304,20 @@
       <c r="CD12" s="5">
         <v>42089</v>
       </c>
+      <c r="CE12" s="5">
+        <v>41620</v>
+      </c>
+      <c r="CF12" s="5">
+        <v>41587</v>
+      </c>
+      <c r="CG12" s="5">
+        <v>40093</v>
+      </c>
+      <c r="CH12" s="5">
+        <v>40049</v>
+      </c>
     </row>
-    <row r="13" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
@@ -37106,8 +37564,20 @@
       <c r="CD13" s="5">
         <v>39327</v>
       </c>
+      <c r="CE13" s="5">
+        <v>40033</v>
+      </c>
+      <c r="CF13" s="5">
+        <v>41923</v>
+      </c>
+      <c r="CG13" s="5">
+        <v>42341</v>
+      </c>
+      <c r="CH13" s="5">
+        <v>42630</v>
+      </c>
     </row>
-    <row r="14" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>12</v>
       </c>
@@ -37354,8 +37824,20 @@
       <c r="CD14" s="5">
         <v>15254</v>
       </c>
+      <c r="CE14" s="5">
+        <v>15546</v>
+      </c>
+      <c r="CF14" s="5">
+        <v>15891</v>
+      </c>
+      <c r="CG14" s="5">
+        <v>16351</v>
+      </c>
+      <c r="CH14" s="5">
+        <v>19379</v>
+      </c>
     </row>
-    <row r="15" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
@@ -37602,8 +38084,20 @@
       <c r="CD15" s="5">
         <v>461</v>
       </c>
+      <c r="CE15" s="5">
+        <v>461</v>
+      </c>
+      <c r="CF15" s="5">
+        <v>595</v>
+      </c>
+      <c r="CG15" s="5">
+        <v>595</v>
+      </c>
+      <c r="CH15" s="5">
+        <v>595</v>
+      </c>
     </row>
-    <row r="16" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>14</v>
       </c>
@@ -37850,8 +38344,20 @@
       <c r="CD16" s="5">
         <v>18216</v>
       </c>
+      <c r="CE16" s="5">
+        <v>18250</v>
+      </c>
+      <c r="CF16" s="5">
+        <v>18237</v>
+      </c>
+      <c r="CG16" s="5">
+        <v>18184</v>
+      </c>
+      <c r="CH16" s="5">
+        <v>18550</v>
+      </c>
     </row>
-    <row r="17" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>15</v>
       </c>
@@ -38098,8 +38604,20 @@
       <c r="CD17" s="5">
         <v>6866</v>
       </c>
+      <c r="CE17" s="5">
+        <v>6872</v>
+      </c>
+      <c r="CF17" s="5">
+        <v>6867</v>
+      </c>
+      <c r="CG17" s="5">
+        <v>6703</v>
+      </c>
+      <c r="CH17" s="5">
+        <v>6705</v>
+      </c>
     </row>
-    <row r="18" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
@@ -38346,8 +38864,20 @@
       <c r="CD18" s="5">
         <v>21084</v>
       </c>
+      <c r="CE18" s="5">
+        <v>21098</v>
+      </c>
+      <c r="CF18" s="5">
+        <v>21119</v>
+      </c>
+      <c r="CG18" s="5">
+        <v>18200</v>
+      </c>
+      <c r="CH18" s="5">
+        <v>18213</v>
+      </c>
     </row>
-    <row r="19" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
@@ -38594,8 +39124,20 @@
       <c r="CD19" s="5">
         <v>90473</v>
       </c>
+      <c r="CE19" s="5">
+        <v>84242</v>
+      </c>
+      <c r="CF19" s="5">
+        <v>85377</v>
+      </c>
+      <c r="CG19" s="5">
+        <v>86197</v>
+      </c>
+      <c r="CH19" s="5">
+        <v>86869</v>
+      </c>
     </row>
-    <row r="20" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>18</v>
       </c>
@@ -38842,8 +39384,20 @@
       <c r="CD20" s="5">
         <v>61418</v>
       </c>
+      <c r="CE20" s="5">
+        <v>55134</v>
+      </c>
+      <c r="CF20" s="5">
+        <v>56226</v>
+      </c>
+      <c r="CG20" s="5">
+        <v>57052</v>
+      </c>
+      <c r="CH20" s="5">
+        <v>57697</v>
+      </c>
     </row>
-    <row r="21" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>19</v>
       </c>
@@ -39090,8 +39644,20 @@
       <c r="CD21" s="5">
         <v>277045</v>
       </c>
+      <c r="CE21" s="5">
+        <v>279329</v>
+      </c>
+      <c r="CF21" s="5">
+        <v>346375</v>
+      </c>
+      <c r="CG21" s="5">
+        <v>270962</v>
+      </c>
+      <c r="CH21" s="5">
+        <v>270144</v>
+      </c>
     </row>
-    <row r="22" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>20</v>
       </c>
@@ -39338,8 +39904,20 @@
       <c r="CD22" s="5">
         <v>235999</v>
       </c>
+      <c r="CE22" s="5">
+        <v>237471</v>
+      </c>
+      <c r="CF22" s="5">
+        <v>303999</v>
+      </c>
+      <c r="CG22" s="5">
+        <v>229108</v>
+      </c>
+      <c r="CH22" s="5">
+        <v>228078</v>
+      </c>
     </row>
-    <row r="23" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>21</v>
       </c>
@@ -39586,8 +40164,20 @@
       <c r="CD23" s="5">
         <v>70267</v>
       </c>
+      <c r="CE23" s="5">
+        <v>74131</v>
+      </c>
+      <c r="CF23" s="5">
+        <v>74849</v>
+      </c>
+      <c r="CG23" s="5">
+        <v>80007</v>
+      </c>
+      <c r="CH23" s="5">
+        <v>82610</v>
+      </c>
     </row>
-    <row r="24" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>22</v>
       </c>
@@ -39834,8 +40424,20 @@
       <c r="CD24" s="5">
         <v>1033</v>
       </c>
+      <c r="CE24" s="5">
+        <v>983</v>
+      </c>
+      <c r="CF24" s="5">
+        <v>986</v>
+      </c>
+      <c r="CG24" s="5">
+        <v>940</v>
+      </c>
+      <c r="CH24" s="5">
+        <v>940</v>
+      </c>
     </row>
-    <row r="25" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>23</v>
       </c>
@@ -40082,8 +40684,20 @@
       <c r="CD25" s="5">
         <v>493788</v>
       </c>
+      <c r="CE25" s="5">
+        <v>540174</v>
+      </c>
+      <c r="CF25" s="5">
+        <v>553571</v>
+      </c>
+      <c r="CG25" s="5">
+        <v>499427</v>
+      </c>
+      <c r="CH25" s="5">
+        <v>518963</v>
+      </c>
     </row>
-    <row r="26" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>24</v>
       </c>
@@ -40330,8 +40944,20 @@
       <c r="CD26" s="5">
         <v>491070</v>
       </c>
+      <c r="CE26" s="5">
+        <v>496562</v>
+      </c>
+      <c r="CF26" s="5">
+        <v>485751</v>
+      </c>
+      <c r="CG26" s="5">
+        <v>484007</v>
+      </c>
+      <c r="CH26" s="5">
+        <v>499560</v>
+      </c>
     </row>
-    <row r="27" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>25</v>
       </c>
@@ -40578,8 +41204,20 @@
       <c r="CD27" s="5">
         <v>922287</v>
       </c>
+      <c r="CE27" s="5">
+        <v>925412</v>
+      </c>
+      <c r="CF27" s="5">
+        <v>926525</v>
+      </c>
+      <c r="CG27" s="5">
+        <v>897101</v>
+      </c>
+      <c r="CH27" s="5">
+        <v>897388</v>
+      </c>
     </row>
-    <row r="28" spans="1:82" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:86" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>26</v>
       </c>
@@ -40825,6 +41463,18 @@
       </c>
       <c r="CD28" s="5">
         <v>30720</v>
+      </c>
+      <c r="CE28" s="5">
+        <v>30432</v>
+      </c>
+      <c r="CF28" s="5">
+        <v>30474</v>
+      </c>
+      <c r="CG28" s="5">
+        <v>29871</v>
+      </c>
+      <c r="CH28" s="5">
+        <v>31633</v>
       </c>
     </row>
   </sheetData>
